--- a/customers_prospects/accounts/del-taco/current/Del_Taco_Blue_Sheet.xlsx
+++ b/customers_prospects/accounts/del-taco/current/Del_Taco_Blue_Sheet.xlsx
@@ -790,7 +790,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="12" t="inlineStr">
         <is>
-          <t>Executive working account plan | updated 2026-08-21</t>
+          <t>Executive working account plan | updated 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="C5" s="15" t="inlineStr">
@@ -829,10 +829,14 @@
       </c>
       <c r="D5" s="14" t="inlineStr">
         <is>
-          <t>Todd Vahlsing</t>
-        </is>
-      </c>
-      <c r="E5" s="33" t="inlineStr"/>
+          <t>Maggie Lenhart</t>
+        </is>
+      </c>
+      <c r="E5" s="33" t="inlineStr">
+        <is>
+          <t>Nick Hulayew reported (2026-09-08) that Del Taco is conducting a comprehensive review of its technology stack -- payments, digital menu boards, POS hardware and POS software -- as part of Yadav Enterprises' Project Sunrise turnaround. Maggie Lenhart separately reported (2026-09-29) that Del Taco is evaluating Nova as a new POS, and that Worldpay does not yet have a Nova card-present integration for enterprise merchants.</t>
+        </is>
+      </c>
       <c r="F5" s="34" t="n"/>
       <c r="G5" s="34" t="n"/>
       <c r="H5" s="34" t="n"/>
@@ -911,12 +915,12 @@
       </c>
       <c r="O6" s="27" t="inlineStr">
         <is>
-          <t>[Current read - evidence-based, not assumed]</t>
+          <t>No budget has been confirmed for any workstream; Project Sunrise is a turnaround program but no line item or funding source has been identified.</t>
         </is>
       </c>
       <c r="P6" s="27" t="inlineStr">
         <is>
-          <t>[Next validating step]</t>
+          <t>Confirm budget source, approval path, and whether DMB/payments/POS are funded separately or as one program.</t>
         </is>
       </c>
     </row>
@@ -962,12 +966,12 @@
       </c>
       <c r="O7" s="27" t="inlineStr">
         <is>
-          <t>[Current read - evidence-based, not assumed]</t>
+          <t>Two reported paths: Nick Hulayew's direct relationship with Daniel Mears (introduced via Genius World), and Maggie Lenhart's Worldpay relationship, which also emailed Daniel directly. Neither has yet produced a scheduled discovery meeting.</t>
         </is>
       </c>
       <c r="P7" s="27" t="inlineStr">
         <is>
-          <t>[Next validating step]</t>
+          <t>Convert Nick's promised reconnection and Maggie's email into a scheduled discovery call with Daniel Mears.</t>
         </is>
       </c>
     </row>
@@ -1013,12 +1017,12 @@
       </c>
       <c r="O8" s="27" t="inlineStr">
         <is>
-          <t>[Current read - evidence-based, not assumed]</t>
+          <t>No RFP, RFI, or formal sourcing event exists. Nick described a comprehensive internal review; Maggie reported a separate Nova POS evaluation. Stage, governance, and decision calendar are unconfirmed.</t>
         </is>
       </c>
       <c r="P8" s="27" t="inlineStr">
         <is>
-          <t>[Next validating step]</t>
+          <t>Use first discovery conversation to confirm scope, stage, governance, budget and timeline of the reported review.</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1032,11 @@
           <t>Single sales objective</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr"/>
+      <c r="B9" s="14" t="inlineStr">
+        <is>
+          <t>Convert Nick Hulayew's promised introduction to Daniel Mears and Maggie Lenhart's Worldpay access into a qualified discovery meeting; lead with Project Sunrise business outcomes and position Genius hardware reuse (the Pollo Tropical NCR CX-5 retrofit) as a capital-efficient path into the reported comprehensive review of payments, digital menu boards, POS hardware and POS software. Digital menu boards are the likely first wedge while the broader platform opportunity is qualified in parallel.</t>
+        </is>
+      </c>
       <c r="C9" s="38" t="n"/>
       <c r="D9" s="39" t="n"/>
       <c r="E9" s="36" t="n"/>
@@ -1052,12 +1060,12 @@
       </c>
       <c r="O9" s="27" t="inlineStr">
         <is>
-          <t>[Current read - evidence-based, not assumed]</t>
+          <t>Dean (reported Yadav CTO) is described by Nick Hulayew as a strong Genius champion and advisory-board member, but exact title, surname spelling, and decision authority are unverified.</t>
         </is>
       </c>
       <c r="P9" s="27" t="inlineStr">
         <is>
-          <t>[Next validating step]</t>
+          <t>Validate Dean's exact role and authority; confirm whether he can sponsor or fund this specific opportunity.</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1075,11 @@
           <t>Commercial hypothesis</t>
         </is>
       </c>
-      <c r="B10" s="14" t="inlineStr"/>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>No commercial hypothesis has been priced or proposed. Digital menu boards are judged the likely first wedge per account strategy, but no scope, pricing, or commercial terms exist yet -- this requires direct discovery before any figure can be stated.</t>
+        </is>
+      </c>
       <c r="C10" s="38" t="n"/>
       <c r="D10" s="39" t="n"/>
       <c r="E10" s="40" t="n"/>
@@ -1095,12 +1107,12 @@
       </c>
       <c r="O10" s="27" t="inlineStr">
         <is>
-          <t>[Current read - evidence-based, not assumed]</t>
+          <t>Nick Hulayew (internal, not customer-side) has offered to support calls and the relationship handoff; no customer-side coach is yet verified.</t>
         </is>
       </c>
       <c r="P10" s="27" t="inlineStr">
         <is>
-          <t>[Next validating step]</t>
+          <t>Test Daniel Mears for coach behavior (access, credibility, guidance) once a direct conversation occurs.</t>
         </is>
       </c>
     </row>
@@ -1146,10 +1158,18 @@
           <t>Current state</t>
         </is>
       </c>
-      <c r="B13" s="27" t="inlineStr"/>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Active urgency, unconfirmed buyer</t>
+        </is>
+      </c>
       <c r="C13" s="43" t="n"/>
       <c r="D13" s="44" t="n"/>
-      <c r="E13" s="27" t="inlineStr"/>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Qu won the prior Jack in the Box RFP for POS, but Del Taco's actual adoption was never confirmed and current Yadav intent is unknown; legacy NCR Aloha/MenuLink is reported as the historical back-office/menu layer; Maggie Lenhart separately reports Del Taco is now evaluating Nova as a new POS, and Worldpay does not yet have a Nova card-present integration for enterprise merchants. Nick Hulayew's unconfirmed belief that Anil Yadav is a silent investor in Qu is reported intelligence only, not established fact.</t>
+        </is>
+      </c>
       <c r="F13" s="45" t="n"/>
       <c r="G13" s="45" t="n"/>
       <c r="H13" s="45" t="n"/>
@@ -1160,14 +1180,22 @@
           <t>Place in funnel</t>
         </is>
       </c>
-      <c r="L13" s="27" t="inlineStr"/>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>Qualify</t>
+        </is>
+      </c>
       <c r="M13" s="27" t="n"/>
       <c r="N13" s="6" t="inlineStr">
         <is>
           <t>Position vs. competition</t>
         </is>
       </c>
-      <c r="O13" s="27" t="inlineStr"/>
+      <c r="O13" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="P13" s="27" t="n"/>
     </row>
     <row r="14" ht="42" customHeight="1">
@@ -1176,7 +1204,11 @@
           <t>Reason</t>
         </is>
       </c>
-      <c r="B14" s="27" t="inlineStr"/>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>Yadav's Project Sunrise turnaround (declining same-store sales, transaction counts, and margin inherited at acquisition) creates real modernization pressure, and Nick Hulayew reports an active comprehensive technology review -- but no customer-side buyer, budget, or sourcing process has been confirmed yet, so urgency has not converted to a qualified opportunity.</t>
+        </is>
+      </c>
       <c r="C14" s="43" t="n"/>
       <c r="D14" s="44" t="n"/>
       <c r="E14" s="47" t="n"/>
@@ -1186,7 +1218,11 @@
           <t>Customer priority</t>
         </is>
       </c>
-      <c r="L14" s="27" t="inlineStr"/>
+      <c r="L14" s="27" t="inlineStr">
+        <is>
+          <t>Unconfirmed</t>
+        </is>
+      </c>
       <c r="M14" s="27" t="n"/>
       <c r="N14" s="6" t="inlineStr">
         <is>
@@ -1206,7 +1242,11 @@
           <t>Timing</t>
         </is>
       </c>
-      <c r="B15" s="27" t="inlineStr"/>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>Worldpay's contract extension (signed 2026-09-03) removed a renewal-period coordination constraint and opened a cleaner window for joint discovery.</t>
+        </is>
+      </c>
       <c r="C15" s="43" t="n"/>
       <c r="D15" s="44" t="n"/>
       <c r="E15" s="49" t="n"/>
@@ -1220,14 +1260,22 @@
           <t>Critical test</t>
         </is>
       </c>
-      <c r="L15" s="27" t="inlineStr"/>
+      <c r="L15" s="27" t="inlineStr">
+        <is>
+          <t>Does direct customer discovery confirm a real, funded modernization event with a credible Genius wedge and an accountable buyer?</t>
+        </is>
+      </c>
       <c r="M15" s="27" t="n"/>
       <c r="N15" s="6" t="inlineStr">
         <is>
           <t>Immediate move</t>
         </is>
       </c>
-      <c r="O15" s="27" t="inlineStr"/>
+      <c r="O15" s="27" t="inlineStr">
+        <is>
+          <t>Convert Nick's promised introduction and Maggie's email into a scheduled discovery call with Daniel Mears.</t>
+        </is>
+      </c>
       <c r="P15" s="27" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
@@ -1304,93 +1352,323 @@
       <c r="P18" s="39" t="n"/>
     </row>
     <row r="19" ht="66" customHeight="1">
-      <c r="A19" s="27" t="n"/>
-      <c r="B19" s="27" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="27" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="27" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="27" t="n"/>
-      <c r="I19" s="27" t="n"/>
-      <c r="J19" s="27" t="n"/>
-      <c r="K19" s="27" t="n"/>
+      <c r="A19" s="27" t="inlineStr">
+        <is>
+          <t>Daniel Mears — Reported IT director within the Del Taco technology organization</t>
+        </is>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>U? / T?</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F19" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G19" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Reported IT director; attended Genius World and met Nick Hulayew there. Maggie Lenhart emailed him directly on 2026-09-15 to introduce Todd. No reply or meeting confirmed yet.</t>
+        </is>
+      </c>
+      <c r="J19" s="27" t="inlineStr">
+        <is>
+          <t>Direct relationship through Nick Hulayew; access also attempted through Maggie</t>
+        </is>
+      </c>
+      <c r="K19" s="27" t="inlineStr">
+        <is>
+          <t>Confirm exact title, reporting line, budget authority, and role in the comprehensive technology review.</t>
+        </is>
+      </c>
       <c r="L19" s="43" t="n"/>
       <c r="M19" s="43" t="n"/>
       <c r="N19" s="44" t="n"/>
-      <c r="O19" s="27" t="n"/>
+      <c r="O19" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Nick / Maggie</t>
+        </is>
+      </c>
       <c r="P19" s="44" t="n"/>
     </row>
     <row r="20" ht="66" customHeight="1">
-      <c r="A20" s="27" t="n"/>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="27" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="27" t="n"/>
-      <c r="J20" s="27" t="n"/>
-      <c r="K20" s="27" t="n"/>
+      <c r="A20" s="27" t="inlineStr">
+        <is>
+          <t>Dean — Reported Yadav CTO and Daniel Mears' manager</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="inlineStr">
+        <is>
+          <t>E?</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D20" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F20" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G20" s="27" t="inlineStr">
+        <is>
+          <t>Potentially favorable</t>
+        </is>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="27" t="inlineStr">
+        <is>
+          <t>Reported by Nick Hulayew as Yadav's CTO, a strong Genius advocate, and a Genius customer advisory-board member. Surname spelling, exact title, and decision authority require validation.</t>
+        </is>
+      </c>
+      <c r="J20" s="27" t="inlineStr">
+        <is>
+          <t>Indirect, via Nick Hulayew</t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="inlineStr">
+        <is>
+          <t>Validate surname spelling, exact title, scope, and decision authority.</t>
+        </is>
+      </c>
       <c r="L20" s="43" t="n"/>
       <c r="M20" s="43" t="n"/>
       <c r="N20" s="44" t="n"/>
-      <c r="O20" s="27" t="n"/>
+      <c r="O20" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Nick</t>
+        </is>
+      </c>
       <c r="P20" s="44" t="n"/>
     </row>
     <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="27" t="n"/>
-      <c r="B21" s="27" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="27" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="27" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="27" t="n"/>
-      <c r="I21" s="27" t="n"/>
-      <c r="J21" s="27" t="n"/>
-      <c r="K21" s="27" t="n"/>
+      <c r="A21" s="27" t="inlineStr">
+        <is>
+          <t>Nick Hulayew — Internal relationship path to Daniel Mears and Dean — internal</t>
+        </is>
+      </c>
+      <c r="B21" s="27" t="inlineStr">
+        <is>
+          <t>Internal referrer, not customer-side</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="inlineStr">
+        <is>
+          <t>Not a customer buying influence (internal)</t>
+        </is>
+      </c>
+      <c r="D21" s="27" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+      <c r="E21" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F21" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal referrer)</t>
+        </is>
+      </c>
+      <c r="G21" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal)</t>
+        </is>
+      </c>
+      <c r="H21" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="27" t="inlineStr">
+        <is>
+          <t>Agreed to reconnect with Daniel Mears, continue the Genius World conversation, introduce Todd, and support future calls.</t>
+        </is>
+      </c>
+      <c r="J21" s="27" t="inlineStr">
+        <is>
+          <t>Internal; not a customer decision-maker</t>
+        </is>
+      </c>
+      <c r="K21" s="27" t="inlineStr">
+        <is>
+          <t>Confirm he has followed through on reconnecting with Daniel Mears.</t>
+        </is>
+      </c>
       <c r="L21" s="43" t="n"/>
       <c r="M21" s="43" t="n"/>
       <c r="N21" s="44" t="n"/>
-      <c r="O21" s="27" t="n"/>
+      <c r="O21" s="27" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
       <c r="P21" s="44" t="n"/>
     </row>
     <row r="22" ht="66" customHeight="1">
-      <c r="A22" s="27" t="n"/>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="27" t="n"/>
-      <c r="H22" s="27" t="n"/>
-      <c r="I22" s="27" t="n"/>
-      <c r="J22" s="27" t="n"/>
-      <c r="K22" s="27" t="n"/>
+      <c r="A22" s="27" t="inlineStr">
+        <is>
+          <t>Maggie Lenhart — Worldpay relationship owner — internal (Worldpay)</t>
+        </is>
+      </c>
+      <c r="B22" s="27" t="inlineStr">
+        <is>
+          <t>Internal referrer, not customer-side</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="inlineStr">
+        <is>
+          <t>Not a customer buying influence (internal)</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+      <c r="E22" s="27" t="inlineStr">
+        <is>
+          <t>Strengthen the broader Global Payments relationship and support future cross-sell opportunities.</t>
+        </is>
+      </c>
+      <c r="F22" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal referrer)</t>
+        </is>
+      </c>
+      <c r="G22" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal)</t>
+        </is>
+      </c>
+      <c r="H22" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="27" t="inlineStr">
+        <is>
+          <t>Manages the Del Taco relationship on the Worldpay side; signed the contract extension 2026-09-03; emailed Daniel Mears directly on 2026-09-15 to introduce Todd; reported on 2026-09-29 that Del Taco is evaluating Nova as a new POS.</t>
+        </is>
+      </c>
+      <c r="J22" s="27" t="inlineStr">
+        <is>
+          <t>Direct email / formal Worldpay relationship channel</t>
+        </is>
+      </c>
+      <c r="K22" s="27" t="inlineStr">
+        <is>
+          <t>Coordinate next outreach step with Nick and Todd; track Nova integration status.</t>
+        </is>
+      </c>
       <c r="L22" s="43" t="n"/>
       <c r="M22" s="43" t="n"/>
       <c r="N22" s="44" t="n"/>
-      <c r="O22" s="27" t="n"/>
+      <c r="O22" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Maggie</t>
+        </is>
+      </c>
       <c r="P22" s="44" t="n"/>
     </row>
     <row r="23" ht="66" customHeight="1">
-      <c r="A23" s="27" t="n"/>
-      <c r="B23" s="27" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="27" t="n"/>
-      <c r="G23" s="27" t="n"/>
-      <c r="H23" s="27" t="n"/>
-      <c r="I23" s="27" t="n"/>
-      <c r="J23" s="27" t="n"/>
-      <c r="K23" s="27" t="n"/>
+      <c r="A23" s="27" t="inlineStr">
+        <is>
+          <t>David OCallaghan — Vice President, Company Operations</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>U?</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D23" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E23" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F23" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="G23" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="H23" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="27" t="inlineStr">
+        <is>
+          <t>Connected with Todd on LinkedIn and agreed to a meeting, then redirected to Del Taco's Innovation/IT team; that introduction did not produce a scheduled meeting. Todd later followed up directly, copying AE Nicole Payne.</t>
+        </is>
+      </c>
+      <c r="J23" s="27" t="inlineStr">
+        <is>
+          <t>Weak; prior LinkedIn contact did not convert to a meeting</t>
+        </is>
+      </c>
+      <c r="K23" s="27" t="inlineStr">
+        <is>
+          <t>Follow up on the pending informal operations conversation request.</t>
+        </is>
+      </c>
       <c r="L23" s="43" t="n"/>
       <c r="M23" s="43" t="n"/>
       <c r="N23" s="44" t="n"/>
-      <c r="O23" s="27" t="n"/>
+      <c r="O23" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Nicole Payne</t>
+        </is>
+      </c>
       <c r="P23" s="44" t="n"/>
     </row>
     <row r="24" ht="66" customHeight="1">
@@ -1508,58 +1786,118 @@
       </c>
     </row>
     <row r="33" ht="44" customHeight="1">
-      <c r="A33" s="27" t="n"/>
+      <c r="A33" s="27" t="inlineStr">
+        <is>
+          <t>Two coordinated internal paths into the account: Maggie Lenhart's trusted Worldpay relationship (contract extension signed 2026-09-03) and Nick Hulayew's direct relationship with reported IT director Daniel Mears via Genius World.</t>
+        </is>
+      </c>
       <c r="B33" s="43" t="n"/>
       <c r="C33" s="43" t="n"/>
       <c r="D33" s="44" t="n"/>
-      <c r="E33" s="27" t="n"/>
+      <c r="E33" s="27" t="inlineStr">
+        <is>
+          <t>Coordinate the two paths into one outreach rather than running them in parallel.</t>
+        </is>
+      </c>
       <c r="F33" s="43" t="n"/>
       <c r="G33" s="43" t="n"/>
       <c r="H33" s="43" t="n"/>
       <c r="I33" s="43" t="n"/>
       <c r="J33" s="44" t="n"/>
-      <c r="K33" s="27" t="n"/>
+      <c r="K33" s="27" t="inlineStr">
+        <is>
+          <t>Nick reconnects with Daniel; Maggie's 2026-09-15 email introduction to Daniel is already sent.</t>
+        </is>
+      </c>
       <c r="L33" s="43" t="n"/>
       <c r="M33" s="44" t="n"/>
-      <c r="N33" s="27" t="n"/>
+      <c r="N33" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Nick / Maggie</t>
+        </is>
+      </c>
       <c r="O33" s="44" t="n"/>
-      <c r="P33" s="27" t="n"/>
+      <c r="P33" s="27" t="inlineStr">
+        <is>
+          <t>Discovery call scheduled</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="44" customHeight="1">
-      <c r="A34" s="27" t="n"/>
+      <c r="A34" s="27" t="inlineStr">
+        <is>
+          <t>Pollo Tropical's NCR CX-5 Windows-to-Android retrofit running Genius is a real, citable proof point that existing NCR hardware can potentially be reused rather than replaced -- directly relevant to Del Taco's reported capital constraints.</t>
+        </is>
+      </c>
       <c r="B34" s="43" t="n"/>
       <c r="C34" s="43" t="n"/>
       <c r="D34" s="44" t="n"/>
-      <c r="E34" s="27" t="n"/>
+      <c r="E34" s="27" t="inlineStr">
+        <is>
+          <t>Prepare the Pollo Tropical retrofit as evidence in the first discovery conversation.</t>
+        </is>
+      </c>
       <c r="F34" s="43" t="n"/>
       <c r="G34" s="43" t="n"/>
       <c r="H34" s="43" t="n"/>
       <c r="I34" s="43" t="n"/>
       <c r="J34" s="44" t="n"/>
-      <c r="K34" s="27" t="n"/>
+      <c r="K34" s="27" t="inlineStr">
+        <is>
+          <t>Validate Del Taco's current NCR estate (model, age, condition) before presenting it as a fit.</t>
+        </is>
+      </c>
       <c r="L34" s="43" t="n"/>
       <c r="M34" s="44" t="n"/>
-      <c r="N34" s="27" t="n"/>
+      <c r="N34" s="27" t="inlineStr">
+        <is>
+          <t>Todd / solution lead</t>
+        </is>
+      </c>
       <c r="O34" s="44" t="n"/>
-      <c r="P34" s="27" t="n"/>
+      <c r="P34" s="27" t="inlineStr">
+        <is>
+          <t>First discovery conversation</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="44" customHeight="1">
-      <c r="A35" s="27" t="n"/>
+      <c r="A35" s="27" t="inlineStr">
+        <is>
+          <t>Dean (reported Yadav CTO) is described by Nick Hulayew as a strong Genius advocate and Genius customer advisory-board member, though his exact title and decision authority require validation.</t>
+        </is>
+      </c>
       <c r="B35" s="43" t="n"/>
       <c r="C35" s="43" t="n"/>
       <c r="D35" s="44" t="n"/>
-      <c r="E35" s="27" t="n"/>
+      <c r="E35" s="27" t="inlineStr">
+        <is>
+          <t>Use Nick's relationship with Dean to seek an internal introduction or endorsement.</t>
+        </is>
+      </c>
       <c r="F35" s="43" t="n"/>
       <c r="G35" s="43" t="n"/>
       <c r="H35" s="43" t="n"/>
       <c r="I35" s="43" t="n"/>
       <c r="J35" s="44" t="n"/>
-      <c r="K35" s="27" t="n"/>
+      <c r="K35" s="27" t="inlineStr">
+        <is>
+          <t>Validate Dean's authority before relying on his advocacy in any commercial conversation.</t>
+        </is>
+      </c>
       <c r="L35" s="43" t="n"/>
       <c r="M35" s="44" t="n"/>
-      <c r="N35" s="27" t="n"/>
+      <c r="N35" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Nick</t>
+        </is>
+      </c>
       <c r="O35" s="44" t="n"/>
-      <c r="P35" s="27" t="n"/>
+      <c r="P35" s="27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="44" customHeight="1">
       <c r="A36" s="27" t="n"/>
@@ -1587,76 +1925,156 @@
       </c>
     </row>
     <row r="39" ht="44" customHeight="1">
-      <c r="A39" s="27" t="n"/>
+      <c r="A39" s="27" t="inlineStr">
+        <is>
+          <t>Post-acquisition authority is still being established; Jack in the Box-era contracts and stakeholder assumptions (Rob Stevens, Dana King) may no longer apply under Yadav.</t>
+        </is>
+      </c>
       <c r="B39" s="43" t="n"/>
       <c r="C39" s="43" t="n"/>
       <c r="D39" s="44" t="n"/>
-      <c r="E39" s="27" t="n"/>
+      <c r="E39" s="27" t="inlineStr">
+        <is>
+          <t>Treat every pre-acquisition relationship as unverified until confirmed under current Yadav leadership.</t>
+        </is>
+      </c>
       <c r="F39" s="43" t="n"/>
       <c r="G39" s="43" t="n"/>
       <c r="H39" s="43" t="n"/>
       <c r="I39" s="43" t="n"/>
       <c r="J39" s="44" t="n"/>
-      <c r="K39" s="27" t="n"/>
+      <c r="K39" s="27" t="inlineStr">
+        <is>
+          <t>Validate current org chart and decision authority before advancing any commercial position.</t>
+        </is>
+      </c>
       <c r="L39" s="43" t="n"/>
       <c r="M39" s="44" t="n"/>
-      <c r="N39" s="27" t="n"/>
+      <c r="N39" s="27" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
       <c r="O39" s="44" t="n"/>
-      <c r="P39" s="27" t="n"/>
+      <c r="P39" s="27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="40" ht="44" customHeight="1">
-      <c r="A40" s="27" t="n"/>
+      <c r="A40" s="27" t="inlineStr">
+        <is>
+          <t>Qu's prior RFP win and the newly reported Nova POS evaluation mean the POS layer may already be contested or moving toward a different vendor; Worldpay does not yet have a Nova card-present integration for enterprise merchants, which is a real technical gap if Nova is selected.</t>
+        </is>
+      </c>
       <c r="B40" s="43" t="n"/>
       <c r="C40" s="43" t="n"/>
       <c r="D40" s="44" t="n"/>
-      <c r="E40" s="27" t="n"/>
+      <c r="E40" s="27" t="inlineStr">
+        <is>
+          <t>Clarify whether DMB can proceed independently of the POS decision, and track the Worldpay/Nova integration status.</t>
+        </is>
+      </c>
       <c r="F40" s="43" t="n"/>
       <c r="G40" s="43" t="n"/>
       <c r="H40" s="43" t="n"/>
       <c r="I40" s="43" t="n"/>
       <c r="J40" s="44" t="n"/>
-      <c r="K40" s="27" t="n"/>
+      <c r="K40" s="27" t="inlineStr">
+        <is>
+          <t>Separate the DMB wedge from the POS outcome in any proposal; monitor the Nova integration timeline with Maggie.</t>
+        </is>
+      </c>
       <c r="L40" s="43" t="n"/>
       <c r="M40" s="44" t="n"/>
-      <c r="N40" s="27" t="n"/>
+      <c r="N40" s="27" t="inlineStr">
+        <is>
+          <t>Todd / Maggie</t>
+        </is>
+      </c>
       <c r="O40" s="44" t="n"/>
-      <c r="P40" s="27" t="n"/>
+      <c r="P40" s="27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="41" ht="44" customHeight="1">
-      <c r="A41" s="27" t="n"/>
+      <c r="A41" s="27" t="inlineStr">
+        <is>
+          <t>Several internally reported stakeholder names, titles, and authority levels (Daniel Mears, Dean, Dana King, Rob Stevens) remain unverified and must not be used externally before confirmation.</t>
+        </is>
+      </c>
       <c r="B41" s="43" t="n"/>
       <c r="C41" s="43" t="n"/>
       <c r="D41" s="44" t="n"/>
-      <c r="E41" s="27" t="n"/>
+      <c r="E41" s="27" t="inlineStr">
+        <is>
+          <t>Confirm each name, title, and authority level directly before any customer-facing reference.</t>
+        </is>
+      </c>
       <c r="F41" s="43" t="n"/>
       <c r="G41" s="43" t="n"/>
       <c r="H41" s="43" t="n"/>
       <c r="I41" s="43" t="n"/>
       <c r="J41" s="44" t="n"/>
-      <c r="K41" s="27" t="n"/>
+      <c r="K41" s="27" t="inlineStr">
+        <is>
+          <t>First discovery conversation should validate the org chart.</t>
+        </is>
+      </c>
       <c r="L41" s="43" t="n"/>
       <c r="M41" s="44" t="n"/>
-      <c r="N41" s="27" t="n"/>
+      <c r="N41" s="27" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
       <c r="O41" s="44" t="n"/>
-      <c r="P41" s="27" t="n"/>
+      <c r="P41" s="27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="42" ht="44" customHeight="1">
-      <c r="A42" s="27" t="n"/>
+      <c r="A42" s="27" t="inlineStr">
+        <is>
+          <t>Nick Hulayew's belief that Anil Yadav is a silent investor in Qu, and that this influenced the prior Jack in the Box decision, is unconfirmed competitive intelligence and must never be presented externally as fact.</t>
+        </is>
+      </c>
       <c r="B42" s="43" t="n"/>
       <c r="C42" s="43" t="n"/>
       <c r="D42" s="44" t="n"/>
-      <c r="E42" s="27" t="n"/>
+      <c r="E42" s="27" t="inlineStr">
+        <is>
+          <t>Hold this internally as a risk to monitor, not a talking point.</t>
+        </is>
+      </c>
       <c r="F42" s="43" t="n"/>
       <c r="G42" s="43" t="n"/>
       <c r="H42" s="43" t="n"/>
       <c r="I42" s="43" t="n"/>
       <c r="J42" s="44" t="n"/>
-      <c r="K42" s="27" t="n"/>
+      <c r="K42" s="27" t="inlineStr">
+        <is>
+          <t>Do not reference the Yadav-Qu relationship in any customer-facing material without independent confirmation.</t>
+        </is>
+      </c>
       <c r="L42" s="43" t="n"/>
       <c r="M42" s="44" t="n"/>
-      <c r="N42" s="27" t="n"/>
+      <c r="N42" s="27" t="inlineStr">
+        <is>
+          <t>Todd</t>
+        </is>
+      </c>
       <c r="O42" s="44" t="n"/>
-      <c r="P42" s="27" t="n"/>
+      <c r="P42" s="27" t="inlineStr">
+        <is>
+          <t>Open</t>
+        </is>
+      </c>
     </row>
     <row r="43" ht="44" customHeight="1">
       <c r="A43" s="27" t="n"/>
@@ -2428,94 +2846,274 @@
       </c>
     </row>
     <row r="5" ht="66" customHeight="1">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
-      <c r="E5" s="27" t="n"/>
-      <c r="F5" s="27" t="n"/>
-      <c r="G5" s="27" t="n"/>
-      <c r="H5" s="27" t="n"/>
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>Identity &amp; heritage</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Mexican quick-service restaurant, founded 1964, headquartered in Lake Forest, California.</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Long-established regional brand now under new ownership and a named turnaround program.</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E5" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F5" s="27" t="inlineStr"/>
+      <c r="G5" s="27" t="inlineStr"/>
+      <c r="H5" s="27" t="inlineStr"/>
     </row>
     <row r="6" ht="66" customHeight="1">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="27" t="n"/>
-      <c r="H6" s="27" t="n"/>
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>Ownership</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Acquired by Yadav Enterprises from Jack in the Box, closed 2025-12-22, for approximately $119 million after customary adjustments.</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Post-acquisition authority is still being established; pre-acquisition relationships and contracts require revalidation.</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E6" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F6" s="27" t="inlineStr"/>
+      <c r="G6" s="27" t="inlineStr"/>
+      <c r="H6" s="27" t="inlineStr"/>
     </row>
     <row r="7" ht="66" customHeight="1">
-      <c r="A7" s="27" t="n"/>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
-      <c r="E7" s="27" t="n"/>
-      <c r="F7" s="27" t="n"/>
-      <c r="G7" s="27" t="n"/>
-      <c r="H7" s="27" t="n"/>
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>U.S. footprint</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>576 restaurants at FY2025 year-end: 132 company-operated, 444 franchised. Fiscal 2025 systemwide sales of $918.8 million.</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>A majority-franchised estate means technology decisions likely require brand-standard mandates to reach most units.</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E7" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F7" s="27" t="inlineStr"/>
+      <c r="G7" s="27" t="inlineStr"/>
+      <c r="H7" s="27" t="inlineStr"/>
     </row>
     <row r="8" ht="66" customHeight="1">
-      <c r="A8" s="27" t="n"/>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="27" t="n"/>
-      <c r="H8" s="27" t="n"/>
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>Current pursuit</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Executing an 18-month post-acquisition turnaround, 'Project Sunrise,' centered on food quality, operational simplification, value, guest trust, menu innovation, catering expansion, and loyalty.</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Turnaround programs create real modernization pressure but also budget scrutiny; any pitch should tie directly to Project Sunrise's own stated outcomes.</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E8" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F8" s="27" t="inlineStr"/>
+      <c r="G8" s="27" t="inlineStr"/>
+      <c r="H8" s="27" t="inlineStr"/>
     </row>
     <row r="9" ht="66" customHeight="1">
-      <c r="A9" s="27" t="n"/>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="27" t="n"/>
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>U.S. leadership</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>Anil Yadav, CEO, Yadav Enterprises.</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Senior owner-executive publicly accountable for the turnaround and scalability.</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E9" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F9" s="27" t="inlineStr"/>
+      <c r="G9" s="27" t="inlineStr"/>
+      <c r="H9" s="27" t="inlineStr"/>
     </row>
     <row r="10" ht="66" customHeight="1">
-      <c r="A10" s="27" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>U.S. leadership</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Ulyses Camacho, Chief Transformation Officer, Del Taco / Yadav Enterprises.</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Leads unit execution, cost optimization, and systems modernization -- a likely internal sponsor for any technology initiative tied to Project Sunrise.</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F10" s="27" t="inlineStr"/>
+      <c r="G10" s="27" t="inlineStr"/>
+      <c r="H10" s="27" t="inlineStr"/>
     </row>
     <row r="11" ht="66" customHeight="1">
-      <c r="A11" s="27" t="n"/>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>U.S. leadership</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>Noah Chillingworth, Chief Marketing Officer, Del Taco.</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Owns brand strategy, digital and loyalty platforms, and guest insight -- relevant to any digital menu board or loyalty-adjacent pitch.</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F11" s="27" t="inlineStr"/>
+      <c r="G11" s="27" t="inlineStr"/>
+      <c r="H11" s="27" t="inlineStr"/>
     </row>
     <row r="12" ht="66" customHeight="1">
-      <c r="A12" s="27" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Economics / scale</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Fiscal 2025: system same-store sales declined 3.7%, company-store transactions declined 6.9%, and restaurant-level margin was 11.1%. 14 restaurants opened, 32 closed.</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>The inherited operating baseline was pressured, which is the explicit driver behind Project Sunrise and a credible reason for a modernization conversation.</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F12" s="27" t="inlineStr"/>
+      <c r="G12" s="27" t="inlineStr"/>
+      <c r="H12" s="27" t="inlineStr"/>
     </row>
     <row r="13" ht="66" customHeight="1">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Relationship history</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Del Taco previously evaluated Genius for digital menu boards under Jack in the Box ownership; the effort went quiet around the divestiture when the desired system-on-chip approach did not align cleanly with the Genius solution at the time.</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>There is real prior-cycle context and relationship history to draw on, but it is retrospective and must be revalidated under current Yadav leadership, not presented as still-active interest.</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="F13" s="27" t="inlineStr"/>
+      <c r="G13" s="27" t="inlineStr"/>
+      <c r="H13" s="27" t="inlineStr"/>
     </row>
     <row r="14" ht="66" customHeight="1">
       <c r="A14" s="27" t="n"/>
@@ -2670,82 +3268,202 @@
       </c>
     </row>
     <row r="5" ht="68" customHeight="1">
-      <c r="A5" s="27" t="n"/>
-      <c r="B5" s="27" t="n"/>
-      <c r="C5" s="27" t="n"/>
-      <c r="D5" s="27" t="n"/>
+      <c r="A5" s="27" t="inlineStr">
+        <is>
+          <t>payments</t>
+        </is>
+      </c>
+      <c r="B5" s="27" t="inlineStr">
+        <is>
+          <t>Worldpay</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="inlineStr">
+        <is>
+          <t>Contract extension signed 2026-09-03 after an approximately nine-month process.</t>
+        </is>
+      </c>
+      <c r="D5" s="27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E5" s="27" t="n"/>
       <c r="F5" s="27" t="n"/>
       <c r="G5" s="27" t="n"/>
       <c r="H5" s="27" t="n"/>
       <c r="I5" s="27" t="n"/>
       <c r="J5" s="27" t="n"/>
-      <c r="K5" s="27" t="n"/>
+      <c r="K5" s="27" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="68" customHeight="1">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="27" t="n"/>
-      <c r="D6" s="27" t="n"/>
+      <c r="A6" s="27" t="inlineStr">
+        <is>
+          <t>loyalty / digital ordering</t>
+        </is>
+      </c>
+      <c r="B6" s="27" t="inlineStr">
+        <is>
+          <t>Olo</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="inlineStr">
+        <is>
+          <t>Reported as in use; specific modules require validation.</t>
+        </is>
+      </c>
+      <c r="D6" s="27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
       <c r="E6" s="27" t="n"/>
       <c r="F6" s="27" t="n"/>
       <c r="G6" s="27" t="n"/>
       <c r="H6" s="27" t="n"/>
       <c r="I6" s="27" t="n"/>
       <c r="J6" s="27" t="n"/>
-      <c r="K6" s="27" t="n"/>
+      <c r="K6" s="27" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="68" customHeight="1">
-      <c r="A7" s="27" t="n"/>
-      <c r="B7" s="27" t="n"/>
-      <c r="C7" s="27" t="n"/>
-      <c r="D7" s="27" t="n"/>
+      <c r="A7" s="27" t="inlineStr">
+        <is>
+          <t>POS / unified commerce</t>
+        </is>
+      </c>
+      <c r="B7" s="27" t="inlineStr">
+        <is>
+          <t>Qu</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t>Won the prior Jack in the Box RFP; Del Taco adoption was never confirmed and current Yadav intent is unknown.</t>
+        </is>
+      </c>
+      <c r="D7" s="27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
       <c r="E7" s="27" t="n"/>
       <c r="F7" s="27" t="n"/>
       <c r="G7" s="27" t="n"/>
       <c r="H7" s="27" t="n"/>
       <c r="I7" s="27" t="n"/>
       <c r="J7" s="27" t="n"/>
-      <c r="K7" s="27" t="n"/>
+      <c r="K7" s="27" t="inlineStr">
+        <is>
+          <t>Verify</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="68" customHeight="1">
-      <c r="A8" s="27" t="n"/>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
+      <c r="A8" s="27" t="inlineStr">
+        <is>
+          <t>POS / unified commerce (reported new evaluation)</t>
+        </is>
+      </c>
+      <c r="B8" s="27" t="inlineStr">
+        <is>
+          <t>Nova</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="inlineStr">
+        <is>
+          <t>Maggie Lenhart reported Del Taco is looking into Nova as a new POS; Worldpay does not yet have a Nova card-present integration for enterprise merchants and is actively working on one.</t>
+        </is>
+      </c>
+      <c r="D8" s="27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E8" s="27" t="n"/>
       <c r="F8" s="27" t="n"/>
       <c r="G8" s="27" t="n"/>
       <c r="H8" s="27" t="n"/>
       <c r="I8" s="27" t="n"/>
       <c r="J8" s="27" t="n"/>
-      <c r="K8" s="27" t="n"/>
+      <c r="K8" s="27" t="inlineStr">
+        <is>
+          <t>Reported</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="68" customHeight="1">
-      <c r="A9" s="27" t="n"/>
-      <c r="B9" s="27" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
+      <c r="A9" s="27" t="inlineStr">
+        <is>
+          <t>legacy POS / back office</t>
+        </is>
+      </c>
+      <c r="B9" s="27" t="inlineStr">
+        <is>
+          <t>NCR Aloha / MenuLink</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="inlineStr">
+        <is>
+          <t>Historical; internal account history describes a highly legacy menu structure that was difficult to integrate. Current footprint requires validation.</t>
+        </is>
+      </c>
+      <c r="D9" s="27" t="inlineStr">
+        <is>
+          <t>medium</t>
+        </is>
+      </c>
       <c r="E9" s="27" t="n"/>
       <c r="F9" s="27" t="n"/>
       <c r="G9" s="27" t="n"/>
       <c r="H9" s="27" t="n"/>
       <c r="I9" s="27" t="n"/>
       <c r="J9" s="27" t="n"/>
-      <c r="K9" s="27" t="n"/>
+      <c r="K9" s="27" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="68" customHeight="1">
-      <c r="A10" s="27" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>voice AI</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>Presto</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Historical / discontinued.</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
       <c r="E10" s="27" t="n"/>
       <c r="F10" s="27" t="n"/>
       <c r="G10" s="27" t="n"/>
       <c r="H10" s="27" t="n"/>
       <c r="I10" s="27" t="n"/>
       <c r="J10" s="27" t="n"/>
-      <c r="K10" s="27" t="n"/>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>Historical</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="68" customHeight="1">
       <c r="A11" s="27" t="n"/>
@@ -3523,74 +4241,234 @@
       </c>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="27" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Daniel Mears — Reported IT director within the Del Taco technology organization</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>U? / T?</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F10" s="43" t="n"/>
       <c r="G10" s="44" t="n"/>
-      <c r="H10" s="27" t="n"/>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="I10" s="43" t="n"/>
       <c r="J10" s="44" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="27" t="n"/>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>Direct relationship through Nick Hulayew; access also attempted through Maggie</t>
+        </is>
+      </c>
+      <c r="L10" s="27" t="inlineStr">
+        <is>
+          <t>Confirm exact title, reporting line, budget authority, and role in the comprehensive technology review.</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="27" t="n"/>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Dean — Reported Yadav CTO and Daniel Mears' manager</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>E?</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F11" s="43" t="n"/>
       <c r="G11" s="44" t="n"/>
-      <c r="H11" s="27" t="n"/>
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="44" t="n"/>
-      <c r="K11" s="27" t="n"/>
-      <c r="L11" s="27" t="n"/>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>Indirect, via Nick Hulayew</t>
+        </is>
+      </c>
+      <c r="L11" s="27" t="inlineStr">
+        <is>
+          <t>Validate surname spelling, exact title, scope, and decision authority.</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="27" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Nick Hulayew — Internal relationship path to Daniel Mears and Dean</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Internal referrer, not customer-side</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Not a customer buying influence (internal)</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F12" s="43" t="n"/>
       <c r="G12" s="44" t="n"/>
-      <c r="H12" s="27" t="n"/>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal referrer)</t>
+        </is>
+      </c>
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="44" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="27" t="n"/>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>Internal; not a customer decision-maker</t>
+        </is>
+      </c>
+      <c r="L12" s="27" t="inlineStr">
+        <is>
+          <t>Confirm he has followed through on reconnecting with Daniel Mears.</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Maggie Lenhart — Worldpay relationship owner</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Internal referrer, not customer-side</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Not a customer buying influence (internal)</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Strengthen the broader Global Payments relationship and support future cross-sell opportunities.</t>
+        </is>
+      </c>
       <c r="F13" s="43" t="n"/>
       <c r="G13" s="44" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal referrer)</t>
+        </is>
+      </c>
       <c r="I13" s="43" t="n"/>
       <c r="J13" s="44" t="n"/>
-      <c r="K13" s="27" t="n"/>
-      <c r="L13" s="27" t="n"/>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>Direct email / formal Worldpay relationship channel</t>
+        </is>
+      </c>
+      <c r="L13" s="27" t="inlineStr">
+        <is>
+          <t>Coordinate next outreach step with Nick and Todd; track Nova integration status.</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="27" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>David OCallaghan — Vice President, Company Operations</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>U?</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F14" s="43" t="n"/>
       <c r="G14" s="44" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="H14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="I14" s="43" t="n"/>
       <c r="J14" s="44" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="27" t="n"/>
+      <c r="K14" s="27" t="inlineStr">
+        <is>
+          <t>Weak; prior LinkedIn contact did not convert to a meeting</t>
+        </is>
+      </c>
+      <c r="L14" s="27" t="inlineStr">
+        <is>
+          <t>Follow up on the pending informal operations conversation request.</t>
+        </is>
+      </c>
     </row>
     <row r="15" ht="62" customHeight="1">
       <c r="A15" s="27" t="n"/>
@@ -3835,7 +4713,11 @@
       <c r="D5" s="45" t="n"/>
       <c r="E5" s="45" t="n"/>
       <c r="F5" s="46" t="n"/>
-      <c r="G5" s="27" t="inlineStr"/>
+      <c r="G5" s="27" t="inlineStr">
+        <is>
+          <t>Qu won the prior Jack in the Box RFP for POS, but Del Taco's actual adoption was never confirmed and current Yadav intent is unknown; legacy NCR Aloha/MenuLink is reported as the historical back-office/menu layer; Maggie Lenhart separately reports Del Taco is now evaluating Nova as a new POS, and Worldpay does not yet have a Nova card-present integration for enterprise merchants. Nick Hulayew's unconfirmed belief that Anil Yadav is a silent investor in Qu is reported intelligence only, not established fact.</t>
+        </is>
+      </c>
       <c r="H5" s="45" t="n"/>
       <c r="I5" s="45" t="n"/>
       <c r="J5" s="45" t="n"/>
@@ -3909,73 +4791,223 @@
       <c r="L9" s="39" t="n"/>
     </row>
     <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="27" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="A10" s="27" t="inlineStr">
+        <is>
+          <t>Daniel Mears — Reported IT director within the Del Taco technology organization</t>
+        </is>
+      </c>
+      <c r="B10" s="27" t="inlineStr">
+        <is>
+          <t>U? / T?</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E10" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F10" s="44" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="27" t="n"/>
+      <c r="G10" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="27" t="inlineStr">
+        <is>
+          <t>Reported IT director; attended Genius World and met Nick Hulayew there. Maggie Lenhart emailed him directly on 2026-09-15 to introduce Todd. No reply or meeting confirmed yet.</t>
+        </is>
+      </c>
       <c r="I10" s="43" t="n"/>
       <c r="J10" s="44" t="n"/>
-      <c r="K10" s="27" t="n"/>
+      <c r="K10" s="27" t="inlineStr">
+        <is>
+          <t>Confirm exact title, reporting line, budget authority, and role in the comprehensive technology review.</t>
+        </is>
+      </c>
       <c r="L10" s="44" t="n"/>
     </row>
     <row r="11" ht="62" customHeight="1">
-      <c r="A11" s="27" t="n"/>
-      <c r="B11" s="27" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="A11" s="27" t="inlineStr">
+        <is>
+          <t>Dean — Reported Yadav CTO and Daniel Mears' manager</t>
+        </is>
+      </c>
+      <c r="B11" s="27" t="inlineStr">
+        <is>
+          <t>E?</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D11" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E11" s="27" t="inlineStr">
+        <is>
+          <t>Potentially favorable</t>
+        </is>
+      </c>
       <c r="F11" s="44" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="27" t="n"/>
+      <c r="G11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="27" t="inlineStr">
+        <is>
+          <t>Reported by Nick Hulayew as Yadav's CTO, a strong Genius advocate, and a Genius customer advisory-board member. Surname spelling, exact title, and decision authority require validation.</t>
+        </is>
+      </c>
       <c r="I11" s="43" t="n"/>
       <c r="J11" s="44" t="n"/>
-      <c r="K11" s="27" t="n"/>
+      <c r="K11" s="27" t="inlineStr">
+        <is>
+          <t>Validate surname spelling, exact title, scope, and decision authority.</t>
+        </is>
+      </c>
       <c r="L11" s="44" t="n"/>
     </row>
     <row r="12" ht="62" customHeight="1">
-      <c r="A12" s="27" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="A12" s="27" t="inlineStr">
+        <is>
+          <t>Nick Hulayew — Internal relationship path to Daniel Mears and Dean</t>
+        </is>
+      </c>
+      <c r="B12" s="27" t="inlineStr">
+        <is>
+          <t>Internal referrer, not customer-side</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="inlineStr">
+        <is>
+          <t>Not a customer buying influence (internal)</t>
+        </is>
+      </c>
+      <c r="D12" s="27" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+      <c r="E12" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal)</t>
+        </is>
+      </c>
       <c r="F12" s="44" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="27" t="n"/>
+      <c r="G12" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="27" t="inlineStr">
+        <is>
+          <t>Agreed to reconnect with Daniel Mears, continue the Genius World conversation, introduce Todd, and support future calls.</t>
+        </is>
+      </c>
       <c r="I12" s="43" t="n"/>
       <c r="J12" s="44" t="n"/>
-      <c r="K12" s="27" t="n"/>
+      <c r="K12" s="27" t="inlineStr">
+        <is>
+          <t>Confirm he has followed through on reconnecting with Daniel Mears.</t>
+        </is>
+      </c>
       <c r="L12" s="44" t="n"/>
     </row>
     <row r="13" ht="62" customHeight="1">
-      <c r="A13" s="27" t="n"/>
-      <c r="B13" s="27" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
+      <c r="A13" s="27" t="inlineStr">
+        <is>
+          <t>Maggie Lenhart — Worldpay relationship owner</t>
+        </is>
+      </c>
+      <c r="B13" s="27" t="inlineStr">
+        <is>
+          <t>Internal referrer, not customer-side</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t>Not a customer buying influence (internal)</t>
+        </is>
+      </c>
+      <c r="D13" s="27" t="inlineStr">
+        <is>
+          <t>Supportive</t>
+        </is>
+      </c>
+      <c r="E13" s="27" t="inlineStr">
+        <is>
+          <t>Not applicable (internal)</t>
+        </is>
+      </c>
       <c r="F13" s="44" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="27" t="n"/>
+      <c r="G13" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="27" t="inlineStr">
+        <is>
+          <t>Manages the Del Taco relationship on the Worldpay side; signed the contract extension 2026-09-03; emailed Daniel Mears directly on 2026-09-15 to introduce Todd; reported on 2026-09-29 that Del Taco is evaluating Nova as a new POS.</t>
+        </is>
+      </c>
       <c r="I13" s="43" t="n"/>
       <c r="J13" s="44" t="n"/>
-      <c r="K13" s="27" t="n"/>
+      <c r="K13" s="27" t="inlineStr">
+        <is>
+          <t>Coordinate next outreach step with Nick and Todd; track Nova integration status.</t>
+        </is>
+      </c>
       <c r="L13" s="44" t="n"/>
     </row>
     <row r="14" ht="62" customHeight="1">
-      <c r="A14" s="27" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
+      <c r="A14" s="27" t="inlineStr">
+        <is>
+          <t>David OCallaghan — Vice President, Company Operations</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>U?</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="E14" s="27" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
       <c r="F14" s="44" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="27" t="n"/>
+      <c r="G14" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="27" t="inlineStr">
+        <is>
+          <t>Connected with Todd on LinkedIn and agreed to a meeting, then redirected to Del Taco's Innovation/IT team; that introduction did not produce a scheduled meeting. Todd later followed up directly, copying AE Nicole Payne.</t>
+        </is>
+      </c>
       <c r="I14" s="43" t="n"/>
       <c r="J14" s="44" t="n"/>
-      <c r="K14" s="27" t="n"/>
+      <c r="K14" s="27" t="inlineStr">
+        <is>
+          <t>Follow up on the pending informal operations conversation request.</t>
+        </is>
+      </c>
       <c r="L14" s="44" t="n"/>
     </row>
     <row r="15" ht="62" customHeight="1">
@@ -4486,7 +5518,9 @@
           <t>Last reviewed</t>
         </is>
       </c>
-      <c r="E18" s="31" t="n"/>
+      <c r="E18" s="31" t="n">
+        <v>46303</v>
+      </c>
       <c r="F18" s="44" t="n"/>
       <c r="G18" s="6" t="inlineStr">
         <is>
@@ -4495,7 +5529,7 @@
       </c>
       <c r="H18" s="27" t="inlineStr">
         <is>
-          <t>On first dedicated brief, meeting, or document</t>
+          <t>After the first direct discovery conversation with Daniel Mears</t>
         </is>
       </c>
       <c r="I18" s="43" t="n"/>
@@ -4507,7 +5541,11 @@
           <t>Core contributors</t>
         </is>
       </c>
-      <c r="B19" s="27" t="inlineStr"/>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
+          <t>Maggie Lenhart (Worldpay relationship owner); Nick Hulayew (internal relationship path)</t>
+        </is>
+      </c>
       <c r="C19" s="44" t="n"/>
       <c r="D19" s="6" t="inlineStr">
         <is>
@@ -4516,7 +5554,7 @@
       </c>
       <c r="E19" s="27" t="inlineStr">
         <is>
-          <t>Shell only - no dedicated source material found; named in loop L-2026-08-10-005 as part of the first Blue Sheet cohort alongside Pollo Campero and Five Guys. Open RBB loop L-2026-07-23-005 (Del Taco / Yadav Enterprises / Maggie) tracks a related follow-up.</t>
+          <t>Blue Sheet activated from the existing research shell; pre-discovery, no RFP or confirmed buyer yet.</t>
         </is>
       </c>
       <c r="F19" s="44" t="n"/>
@@ -4525,7 +5563,11 @@
           <t>Current critical test</t>
         </is>
       </c>
-      <c r="H19" s="27" t="inlineStr"/>
+      <c r="H19" s="27" t="inlineStr">
+        <is>
+          <t>Does direct customer discovery confirm a real, funded modernization event with a credible Genius wedge and an accountable buyer?</t>
+        </is>
+      </c>
       <c r="I19" s="43" t="n"/>
       <c r="J19" s="44" t="n"/>
     </row>
